--- a/IT23707122.xlsx
+++ b/IT23707122.xlsx
@@ -2,22 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="21359" windowHeight="8174" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Test cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases_Table 1_Table 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,10 +24,174 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial-BoldMT"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="ArialMT"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial-BoldMT"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -41,7 +203,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -50,17 +212,212 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF2FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2FB"/>
+        <bgColor rgb="FFEAF2FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +431,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -84,62 +441,301 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="61">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="10"/>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="2"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="7"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="8"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="21" fillId="33" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="22" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="23" fillId="35" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="22" fillId="36" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="24" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="25" fillId="37" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="24" fillId="38" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="25" fillId="38" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="61">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="RowLevel_1" xfId="1" builtinId="1"/>
+    <cellStyle name="ColLevel_1" xfId="2" builtinId="2"/>
+    <cellStyle name="RowLevel_2" xfId="3" builtinId="1"/>
+    <cellStyle name="ColLevel_2" xfId="4" builtinId="2"/>
+    <cellStyle name="RowLevel_3" xfId="5" builtinId="1"/>
+    <cellStyle name="ColLevel_3" xfId="6" builtinId="2"/>
+    <cellStyle name="RowLevel_4" xfId="7" builtinId="1"/>
+    <cellStyle name="ColLevel_4" xfId="8" builtinId="2"/>
+    <cellStyle name="RowLevel_5" xfId="9" builtinId="1"/>
+    <cellStyle name="ColLevel_5" xfId="10" builtinId="2"/>
+    <cellStyle name="RowLevel_6" xfId="11" builtinId="1"/>
+    <cellStyle name="ColLevel_6" xfId="12" builtinId="2"/>
+    <cellStyle name="RowLevel_7" xfId="13" builtinId="1"/>
+    <cellStyle name="ColLevel_7" xfId="14" builtinId="2"/>
+    <cellStyle name="20% - Accent1" xfId="15" builtinId="30"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="20% - Accent3" xfId="17" builtinId="38"/>
+    <cellStyle name="20% - Accent4" xfId="18" builtinId="42"/>
+    <cellStyle name="20% - Accent5" xfId="19" builtinId="46"/>
+    <cellStyle name="20% - Accent6" xfId="20" builtinId="50"/>
+    <cellStyle name="40% - Accent1" xfId="21" builtinId="31"/>
+    <cellStyle name="40% - Accent2" xfId="22" builtinId="35"/>
+    <cellStyle name="40% - Accent3" xfId="23" builtinId="39"/>
+    <cellStyle name="40% - Accent4" xfId="24" builtinId="43"/>
+    <cellStyle name="40% - Accent5" xfId="25" builtinId="47"/>
+    <cellStyle name="40% - Accent6" xfId="26" builtinId="51"/>
+    <cellStyle name="60% - Accent1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - Accent2" xfId="28" builtinId="36"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
+    <cellStyle name="60% - Accent4" xfId="30" builtinId="44"/>
+    <cellStyle name="60% - Accent5" xfId="31" builtinId="48"/>
+    <cellStyle name="60% - Accent6" xfId="32" builtinId="52"/>
+    <cellStyle name="Accent1" xfId="33" builtinId="29"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="Accent3" xfId="35" builtinId="37"/>
+    <cellStyle name="Accent4" xfId="36" builtinId="41"/>
+    <cellStyle name="Accent5" xfId="37" builtinId="45"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
+    <cellStyle name="Bad" xfId="39" builtinId="27"/>
+    <cellStyle name="Calculation" xfId="40" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="41" builtinId="23"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="43" builtinId="6"/>
+    <cellStyle name="Currency" xfId="44" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="45" builtinId="7"/>
+    <cellStyle name="Explanatory Text" xfId="46" builtinId="53"/>
+    <cellStyle name="Good" xfId="47" builtinId="26"/>
+    <cellStyle name="Heading 1" xfId="48" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="49" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="50" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="51" builtinId="19"/>
+    <cellStyle name="Input" xfId="52" builtinId="20"/>
+    <cellStyle name="Linked Cell" xfId="53" builtinId="24"/>
+    <cellStyle name="Neutral" xfId="54" builtinId="28"/>
+    <cellStyle name="Note" xfId="55" builtinId="10"/>
+    <cellStyle name="Output" xfId="56" builtinId="21"/>
+    <cellStyle name="Percent" xfId="57" builtinId="5"/>
+    <cellStyle name="Title" xfId="58" builtinId="15"/>
+    <cellStyle name="Total" xfId="59" builtinId="25"/>
+    <cellStyle name="Warning Text" xfId="60" builtinId="11"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -222,44 +818,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -286,14 +882,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -320,6 +934,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -331,166 +963,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -501,16 +1109,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="15.125" customWidth="1" min="1" max="1"/>
+    <col width="16.38671875" customWidth="1" min="2" max="2"/>
+    <col width="48.98046875" customWidth="1" min="3" max="5"/>
+    <col width="11.703125" customWidth="1" min="6" max="6"/>
+    <col width="42.13671875" customWidth="1" min="7" max="7"/>
+    <col width="67.7109375" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -566,19 +1172,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>mokada meka karanne?</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>මොකද මේකට කරන්නේ?</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>badu koheda thibune machan?</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>බඩු කොහේද තිබුණේ මචං?</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>මොකද මේක කරන්නේ?</t>
+          <t>බඩු කොහෙද තිබ්බේ මචන්?</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -586,14 +1192,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Question forms</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: The overall message is a question asking 'what is this doing?'</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The overall message is phrased as a question asking where something was kept</t>
         </is>
       </c>
     </row>
@@ -608,19 +1214,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>oya kiyannako api kohomada denna ona ekk?</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>ඔයා කියන්නකෝ අපිට කොහොමද දෙන්න ඕන එක?</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>api kawadada Colombo yanne, ticket eka book kala da?</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>අපි කවදාද Colombo යන්නේ, ticket එක book කළා ද?</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>ඔයා කියන්නකෝ අපි කොහොමද දෙන්න ඕන එකක්?</t>
+          <t>අපි කවදාද Colombo යන්නේ, ticket එක book කළාද?</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -628,14 +1234,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Question forms</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: The input is an indirect question asking how to give something</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: The input is a question asking when they are going and whether the ticket was booked</t>
         </is>
       </c>
     </row>
@@ -650,19 +1256,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Ammata kiyanna mama enne newei kiyala.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>අම්මාට කියන්න මම එන්නේ නෑ කියලා.</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Thatu kiyanna api late wenawa kiyala.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>තාත්තට කියන්න අපි late වෙනවා කියලා.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>අම්මට කියන්න මම එන්නේ නෙවෙයි කියලා.</t>
+          <t>තාත්තතට කියන්න අපි late වෙනවා කියලා.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -670,14 +1276,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Command forms</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: The sentence gives a direct instruction to tell someone something</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The sentence is a direct command to tell father they are running late</t>
         </is>
       </c>
     </row>
@@ -692,19 +1298,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Bohoma avul unata, tikak inna, mama enavai.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>බොහොම අවුල් උනාට, ටිකක් ඉන්න, මම එනවා.</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Eka karanna epa, mama kiyannakam inna.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ඒක කරන්න එපා, මම කියනකම් ඉන්න.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>බොහොම අවුල් වුණාට, ටිකක් ඉන්න, මම එනවායි.</t>
+          <t>ඒක කරන්න එපා, මම කියන්නකම් ඉන්න.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -712,14 +1318,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Command forms</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'tikak inna' is a command telling someone to wait</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'karanna epa' and 'inna' are commands telling someone not to do it and to wait</t>
         </is>
       </c>
     </row>
@@ -734,19 +1340,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Kohomada machan, hodatama innawada?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>කොහොමද මචං, හොඳාටම ඉන්නවද?</t>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Machan, kohomada bung, hodatama da?</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>මචං, කොහොමද බං, හොඳ ද?</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>කොහොමද මචං, හොදටම ඉන්නවද?</t>
+          <t>මචන්, කොහොමද බන්, හොදාටම ද?</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -754,19 +1360,19 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Greetings</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: The input is a greeting asking how the person is doing</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The input is a casual greeting among friends asking how they are</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Neg_0006</t>
         </is>
@@ -776,19 +1382,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Ayya kohomada, wage thiyanawada?</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>අයියා කොහොමද, වේජ් තියෙනවද?</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Happy Birthday nangi, subapathwewa obe life eka godak hoda wewa!</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Happy Birthday නංගි, සුභපැතුවේ ඔබේ life එක ගොඩක් හොඳ වේවා!</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>අයියා කොහොමද, wage තියෙනවද?</t>
+          <t>Happy Birthday නංගි, සුභ පතනවා ඔබේ life එක ගොඩක් හොඳ වේවා!</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -796,14 +1402,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Greetings</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Rationale: The input is a greeting asking how someone is doing; 'wage' is incorrectly left in English instead of being transliterated to Sinhala</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: The input is a birthday greeting with good wishes embedded in Singlish</t>
         </is>
       </c>
     </row>
@@ -818,19 +1424,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Tikak inna, mama number eka kiyannam.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ටිකක් ඉන්න, මම නම්බර් එක කියන්නම්.</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Bro, tikak help karanna puluwan da?</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Bro, ටිකක් help කරන්න පුළුවන් ද?</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>ටිකක් ඉන්න, මම number එක කියන්නම්.</t>
+          <t>Bro, ටිකක් help කරන්න පුළුවන්ද?</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -838,19 +1444,19 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'Tikak inna' is a polite request asking someone to wait</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The sentence is a polite request asking for a little help</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Neg_0008</t>
         </is>
@@ -860,19 +1466,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Tikak inna, mama file eka print karanna yanawa.</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>ටිකක් ඉන්න, මම file එක print කරන්න යනවා.</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Mn yanakota call ekak denna, phone eka silent karala thiyenawa.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>මම යනකොට call එකක් දෙන්න, phone එක silent කරලා තියෙනවා.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>ටිකක් ඉන්න, මම ෆයිල් එක print කරන්න යනවා.</t>
+          <t>මන් යනකොට call එකක් දෙන්න, phone එක silent කරලා තියෙනවා.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -880,14 +1486,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Rationale: This is a polite request to wait; the word 'file' is inconsistently handled — sometimes transliterated and sometimes kept in English</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: The sentence requests someone to give a call when leaving</t>
         </is>
       </c>
     </row>
@@ -902,19 +1508,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Naha, mama danne naha eka gena.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>නෑ, මම දන්නේ නෑ ඒක ගැන.</t>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nope, mama danne naha eka gana.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Nope, මම දන්නේ නෑ ඒක ගැන.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>නැහැ, මම දන්නේ නැහැ ඒක ගැන.</t>
+          <t>Nope, මම දන්නේ නැහැ ඒක ගැන.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -922,14 +1528,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Responses</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: The input is a negative response saying 'No, I do not know about that'</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The input is a negative response using the English word 'Nope' in Singlish</t>
         </is>
       </c>
     </row>
@@ -944,19 +1550,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Ow machan, api yamu kohema hari.</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>ඔව් මචං, අපි යමු කොහේම හරි.</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Aiye, sure, mn ennam.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>අයියේ, sure, මම එන්නම්.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>ඔව් මචන්, අපි යමු කොහෙම හරි.</t>
+          <t>අයියේ, sure, මන් එන්නම්.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -964,14 +1570,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Responses</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: The input is a positive response agreeing to go somewhere</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: The input is a positive confirming response agreeing to come</t>
         </is>
       </c>
     </row>
@@ -986,19 +1592,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Wela wela mama ewa kiyannam.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>වෙලා වෙලා මම එවා කියන්නම්.</t>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Ado ado, mokak da oya karanney?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>අඩෝ අඩෝ, මොකක් ද ඔයා කරන්නේ?</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>වෙලා වෙලා මම ඒවා කියන්නම්.</t>
+          <t>අඩෝ අඩෝ, මොකක්ද ඔයා කරන්නෙ?</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1006,14 +1612,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Repeated Words</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'wela wela' is a repeated word meaning 'time and again'</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Ado ado' is a repeated exclamatory word used in casual Sinhala speech</t>
         </is>
       </c>
     </row>
@@ -1028,19 +1634,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Tikak tikak karanakota hari wela yai.</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>ටිකක් ටිකක් කරනකොට හරි වෙලා යාවි.</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Giya giya thainama, dannawa naha.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ගිය ගිය හැම තැනම, දන්නැ.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>ටිකක් ටිකක් කරනකොට හරි වෙලා යයි.</t>
+          <t>ගිය ගිය තැනාම, දන්නවා නැහැ.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1048,14 +1654,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Repeated Words</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Tikak tikak' is a repeated word meaning 'little by little'</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'Giya giya' is a repeated word meaning 'wherever they went'</t>
         </is>
       </c>
     </row>
@@ -1070,19 +1676,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Ane... mama danne naha mokak karanada?</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>අනේ... මම දන්නේ නෑ මොකක් කරනද?</t>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Aney! mama hithuwe naha oya enawa kiyala...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>අනේ! මම හිතුවේ නෑ ඔයා එනවා කියලා...</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>අනේ... මම දන්නේ නැහැ මොකක් කරනද?</t>
+          <t>අනේ! මම හිතුවේ නැහැ ඔයා එනවා කියලා...</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1090,14 +1696,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Inputs with Punctuation Marks</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: Input uses ellipsis '...' and question mark '?'</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: Input uses exclamation mark '!' and ellipsis '...' within the sentence</t>
         </is>
       </c>
     </row>
@@ -1112,19 +1718,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Hoda! Oya awa, mama hithuwe naha.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>හොඳා! ඔයා ආවා, මම හිතුවේ නෑ.</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Hm... mata thawa tikak time ona, ok da?</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Hm... මට තව ටිකක් time ඕනා, ok ද?</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>හොද! ඔයා ආවා, මම හිතුවේ නැහැ.</t>
+          <t>හ්ම්... මට තව ටිකක් ටයිම් ඕන, ඔක් ද?</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1132,14 +1738,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Inputs with Punctuation Marks</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: Input uses exclamation mark '!' and comma ','</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: Input uses ellipsis '...' and question mark '?' as punctuation marks</t>
         </is>
       </c>
     </row>
@@ -1154,19 +1760,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>mn kohoma hri wlwt yanm kiyala hithn inne.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>මං කොහොම හරි වෙලාවට යන්නම් කියලා හිතන් ඉන්නේ.</t>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>mng oya kiww deyak dannwa, passe ktha krnm.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>මං ඔයා කිව්ව දෙයක් දන්නවා, පස්සේ කතා කරන්නම්.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>මන් කොහොම හරි වෙලාවට යන්නම් කියලා හිතන් ඉන්නේ.</t>
+          <t>මන් ඔයා කිව්ව දෙයක් දන්නවා, පස්සේ කතා කරන්නම්.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1174,14 +1780,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Romanization / Spelling Variants</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: Words like 'mn', 'hri', 'wlwt', 'yanm' are abbreviated variant spellings of Singlish words</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: Words like 'mng', 'kiww', 'dannwa', 'krnm' are heavily abbreviated variant spellings</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1802,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>apii kohomhri eka karanna puluwnda kiyala balamu.</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>අපි කොහොම හරි ඒක කරන්න පුළුවන්ද කියලා බලමු.</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Api heta ymu, tkt ek book krnda pluwn.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>අපි හෙට යමු, ticket එක book කරන්න පුළුවන්.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>අපි කොහොමහරි ඒක කරන්න පුළුවන්ද කියලා බලමු.</t>
+          <t>මන් ඔයා කිව්ව දෙයක් දන්නවා, පස්සේ කතා කරන්නම්.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1216,14 +1822,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Romanization / Spelling Variants</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: Words like 'apii', 'kohomhri', 'puluwnda' are variant romanization spellings of Sinhala words</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: Words like 'ymu', 'tkt', 'krnda', 'pluwn' are abbreviated romanization spellings of Sinhala words</t>
         </is>
       </c>
     </row>
@@ -1238,19 +1844,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>mama ada party ekakata giye bus eken.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>මම අද party එකට ගියේ bus එකෙන්.</t>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>mama ada market eka gihin vegetables gatta.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>මම අද market එකට ගිහින් vegetables ගත්තා.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>මම අද party එකකට ගියේ bus එකෙන්.</t>
+          <t>මම අද market එක ගිහින් vegetables ගත්තා.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1258,14 +1864,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Isolated English Word Insertions in Singlish</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: Single English words 'party' and 'bus' are inserted into Singlish text</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: Single English words 'market' and 'vegetables' are inserted into a Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1280,19 +1886,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>oya ada school eka enne naha kiyala amma kiuwwa.</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>ඔයා අද school එකට එන්නේ නෑ කියලා අම්මා කිව්වා.</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>oya age salary eka raise una da meka month eke?</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ salary එක raise උනා ද මේ month එකේ?</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>ඔයා අද school එක එන්නේ නැහැ කියලා අම්මා කිව්වා.</t>
+          <t>මම අද market එක ගිහින් vegetables ගත්තා.</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1300,14 +1906,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Isolated English Word Insertions in Singlish</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: Single English word 'school' is embedded in the Singlish sentence</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: Single English words 'salary', 'raise', and 'month' are embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1322,19 +1928,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>api short break ekak gangata giyamu kiwwa.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>අපි short break එකක් ගන්න ගියාමු කිව්වා.</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>api last minute plan ekak hadhuwa, yanawada?</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>අපි last minute plan එකක් හැදුවා, යනවාද?</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>අපි ෂෝර්ට් බ්රේක් එකක් ගඟට ගියමු කිව්වා.</t>
+          <t>ඔයා ඇගේ salary එක raise වුණාද මේක month එකේ?</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1342,14 +1948,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Multi-Word English Phrases in Singlish</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'short break' is a multi-word English phrase inserted into a Singlish sentence</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'last minute plan' is a multi-word English phrase inserted into Singlish</t>
         </is>
       </c>
     </row>
@@ -1364,19 +1970,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>api heta field trip ekak yanawa, ready wela inna.</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>අපි හෙට field trip එකකට යනවා, ready වෙලා ඉන්න.</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>heta office eka work from home dha, boss kiuwwa.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>හෙට office එකේ work from home ද, boss කිව්වා.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>අපි හෙට field trip එකක් යනවා, ready වෙලා ඉන්න.</t>
+          <t>අපි last minute plan එකක් හදුවා, යනවද?</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1384,14 +1990,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Multi-Word English Phrases in Singlish</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'field trip' and 'ready wela inna' are multi-word English phrases embedded in Singlish</t>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'work from home' is a multi-word English phrase embedded within a Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1406,19 +2012,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>mage laptop eka charge wennna naha, cable eka nadda.</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>මගේ laptop එක charge වෙන්නේ නෑ, cable එක නැද්ද?</t>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>mage hard disk eka full wela, files delete karanna onee.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>මගේ hard disk එක full වෙලා, files delete කරන්න ඕනේ.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>මගේ laptop එක charge වෙන්න නැහැ, cable එක නැද්ද.</t>
+          <t>මගේ hard disk එක full වෙලා, files delete කරනවා ඕනෙ.</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1426,14 +2032,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>English Digital Terms in Singlish</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'laptop', 'charge', 'cable' are English digital terms used in a Singlish sentence</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'hard disk', 'full', and 'files' are English digital terms used within a Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1448,19 +2054,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>oyage phone eka update kala da, software eka parana.</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>ඔයාගේ phone එක update කළාද, software එක පරණයි.</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>oya screenshot eka send karanna, mama danne naha mokak wenawada kiyala.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ඔයා screenshot එක send කරන්න, මම දන්නේ නෑ මොකක් වෙනවාද කියලා.</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>ඔයාගෙ phone එක update කළා ද, software එක පරණ.</t>
+          <t>ඔයා screenshot එක send කරන්න, මම දන්නේ නැහැ මොකක් වෙනවද කියලා.</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1468,19 +2074,19 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>English Digital Terms in Singlish</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'phone', 'update', 'software' are digital tech English terms within a Singlish sentence</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'screenshot' and 'send' are English digital terms embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Neg_0023</t>
         </is>
@@ -1490,19 +2096,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Facebook eke cover photo eka maru karanda?</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Facebook එකේ cover photo එක මාරු කරනද?</t>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>YouTube eke oya video eka share karanna, godak hodai.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>YouTube එකේ ඔයා video එක share කරන්න, ගොඩක් හොඳයි.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>ෆේස්බුක් එකේ cover photo එක මාරු කරනද?</t>
+          <t>YouTube එකේ ඔය video එක share කරන්න, ගොඩක් හොදයි.</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1510,14 +2116,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Platform/App Names in Singlish</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Rationale: 'Facebook' is a platform name that should remain in English but the system incorrectly transliterates it to Sinhala script 'ෆේස්බුක්'</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'YouTube' is a platform name embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1532,19 +2138,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>api Telegram group eka hadamu class notes share karanna.</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>අපි Telegram group එකක් හදමු class notes share කරන්න.</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>TikTok eke oka viral wela thiyenawa, baluwa da?</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>TikTok එකේ ඒකා viral වෙලා තියෙනවා, බැලුවා ද?</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>අපි Telegram group එක හදමු class notes share කරන්න.</t>
+          <t>YouTube එකේ ඔය video එක share කරන්න, ගොඩක් හොදයි.</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1552,14 +2158,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Platform/App Names in Singlish</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Telegram' is an app name used in a digital context within a Singlish sentence</t>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'TikTok' is a social media app name embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1574,19 +2180,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>mama heta OT karanna ona, boss kiuwwa.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>මම හෙට OT කරන්න ඕනා, boss කිව්වා.</t>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Api DOB eka correct da form eke, check karanna.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>අපේ DOB එක correct ද form එකේ, check කරන්න.</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>මම හෙට OT කරන්න ඕන, boss කිව්වා.</t>
+          <t>TikTok ඒකේ ඕක viral වෙලා තියෙනවා, බැලුවා ද?</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1594,14 +2200,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>English Abbreviations/Acronyms in Singlish</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'OT' is an abbreviation for Overtime used within a Singlish sentence</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'DOB' is an abbreviation for Date of Birth used within a Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1616,19 +2222,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>oya CV eka update kala da new job ekkata apply karanna.</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>ඔයා CV එක update කළාද new job එකකට apply කරන්න.</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Oyata GPA eka kohomada, pass wunada semester eke?</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට GPA එක කොහොමද, pass වුණාද semester එකේ?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>ඔයා CV ඒක update කළා ද new job එක්කට apply කරන්න.</t>
+          <t>අපි DOB ඒක correct ද form එකේ, check කරන්න.</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1636,14 +2242,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>English Abbreviations/Acronyms in Singlish</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'CV' is an acronym for Curriculum Vitae embedded in a Singlish sentence</t>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'GPA' is an academic acronym embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1655,22 +2261,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>mage sub eka awwa, ganna yanawa.</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>මගේ sub එක ආවා, ගන්න යනවා.</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Uni eke canteen eka ada band, kanna yamu, koheda?</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Uni එකේ canteen එක අද band, කන්න යමු, කොහේද?</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>මගේ sub එක අව්ව, ගන්න යනවා.</t>
+          <t>ඔයාට GPA ඒක කොහොමද, පාස් වුණාද semester එකේ?</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1678,14 +2284,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>English Clipped Forms in Singlish</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'sub' is a clipped form of 'submarine sandwich' used within a Singlish sentence</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Uni' is a clipped form of 'University' used within a Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1700,19 +2306,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>api gym ekata yanawa heta, membership eka tiyenawada?</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>අපි හෙට gym එකට යනවා, membership එකක් තියෙනවද?</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>adha arty eka photo session ekak thiyenawa, ready da?</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>අද arty එකේ photo session එකක් තියෙනවා, ready ද?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>අපි gym එකට යනවා හෙට, membership එක තියෙනවද?</t>
+          <t>උනි එකේ canteen එක අද band, කන්න යමු, කොහෙද?</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1720,14 +2326,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>English Clipped Forms in Singlish</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'gym' is a clipped form of 'gymnasium' used in a Singlish sentence</t>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'arty' is a clipped informal form used in casual Singlish conversation</t>
         </is>
       </c>
     </row>
@@ -1742,19 +2348,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>api Kandy walata giye train eken, niyamai.</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>අපි Kandy වලට ගියේ train එකෙන්, නියාමයි.</t>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Negombota yanakota traffic godak thiyanawa, careful wenna.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Negombo වලට යනකොට traffic ගොඩක් තියෙනවා, careful වෙන්න.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>අපි Kandy වලට ගියේ train එකෙන්, නියමයි.</t>
+          <t>උනි එකේ canteen එක අද band, කන්න යමු, කොහෙද?</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1762,14 +2368,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Place Names Embedded in Singlish</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'Kandy' is a Sri Lankan place name embedded in a Singlish sentence</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Negombo' is a Sri Lankan place name embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1784,34 +2390,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>heta api Galle Face eken kana gamu, hodai na?</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>හෙට අපි Galle Face ගිහින් කමු, හොඳයි නෑ?</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>හෙට අපි Galle Face එකෙන් කන ගමු, හොඳයි නෑ?</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Mirissa beach eke sunset eka balanna api yamu heta.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Mirissa beach එකේ sunset එක බලන්න අපි යමු හෙට.</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>මිරිස්ස beach එකේ sunset එක බලන්න අපි යමු හෙට.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Place Names Embedded in Singlish</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Galle Face' is a well-known place in Sri Lanka embedded in a Singlish sentence</t>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'Mirissa' is a Sri Lankan place name embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1826,34 +2432,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Kamal aiye awa da ada practice ekata, dannawada?</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Kamal අයියා ආවාද අද practice එකට, දන්නවද?</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Kamal අයියේ ආවා ද අද practice එකට, දන්නවද?</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Sachini akka, wedding eka April eke da, dannawada?</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Sachini අක්කා, wedding එක April එකේ ද, දන්නවාද?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>සචිනි අක්කා, wedding එක April එකේද, දන්නවද?</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Person Names Embedded in Singlish</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'Kamal' is a personal name embedded in the Singlish sentence</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Sachini' is a personal name embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1868,34 +2474,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Nimal saha Sandya dennama wedding eka cancel karuwa.</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Nimal සහ Sandya දෙන්නාම wedding එක cancel කළා.</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>නිමල් සහ සන්ඩ්යා දෙන්නම wedding එක cancel කරුවා.</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Chamara saha Ruwan dennama project eke naha, avul.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Chamara සහ Ruwan දෙන්නාම project එකේ නෑ, අවුල්.</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>චාමර සහ රුවන් දෙන්නම project එකේ නැහැ, අවුල්.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Person Names Embedded in Singlish</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Nimal' and 'Sandya' are person names embedded in a Singlish sentence</t>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'Chamara' and 'Ruwan' are person names embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1910,34 +2516,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>api gedara inne 5th floor eke, lift naha.</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>අපි ගෙදර ඉන්නේ 5th floor එකේ, lift නෑ.</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>අපි ගෙදර ඉන්නේ 5th floor එකේ, ලිෆ්ට් නැහැ.</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>mama 2nd year eke, thawa 2k witharai units hadanna thiyenne.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>මම 2nd year එකේ, තව 2k විතරයි units හදන්න තියෙන්නේ.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>මම 2nd year එකේ, තව 2ක් විතරයි Units හදන්න තියෙන්නේ.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Inputs with Numbers and Numeric Suffixes</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: '5th' is a number with an ordinal suffix embedded in a Singlish sentence</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: '2nd' has an ordinal suffix and '2k' has a numeric suffix 'k' embedded in Singlish</t>
         </is>
       </c>
     </row>
@@ -1952,34 +2558,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>oya class eke 30k students innawada kohomada manage karanne.</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>ඔයා class එකේ 30k students ඉන්නවද, කොහොමද manage කරන්නේ?</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>ඔය class එකේ 30ක් students ඉන්නවද කොහොමද manage කරන්නේ.</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Oyage phone eka 128GB da, nathnam 256GB eka ganna.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ phone එක 128GB ද, නැත්නම් 256GB එක ගන්න.</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ phone එක 128GB ද, නැත්නම් 256GB එක ගන්න.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Inputs with Numbers and Numeric Suffixes</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: '30k' is a number with numeric suffix 'k' used in a Singlish sentence</t>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: '128GB' and '256GB' are numbers with unit suffixes embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -1994,34 +2600,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>meka LKR 5000 witharai, godak wedagath naha.</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>මේක LKR 5000 විතරයි, ගොඩක් වැදගත් නෑ.</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>මේක LKR 5000 විතරයි, ගොඩක් වැදගත් නැහැ.</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>petrol litre eke gana Rs. 340 una, maru.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>petrol litre එකේ ගාන Rs. 340 උනා, මරු.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>පැට්රෝල් ලිට්රේ එකේ ගාන Rs. 340 උනා, මරු.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Inputs with Currency</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'LKR 5000' is a currency reference embedded in a Singlish sentence</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Rs. 340' is a currency reference embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2036,34 +2642,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>eka class eka USD 200 dawaseka, expensive da?</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>ඒ class එක USD 200 දිනකට, expensive ද?</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>එක class එක USD 200 දවසෙක, expensive ද?</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>e tour package eka AUD 1200, kalin book karanna.</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ඒ tour package එක AUD 1200, කලින් book කරන්න.</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>ඒ tour package එක AUD 1200කලින් book කරන්න.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Inputs with Currency</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'USD 200' is a currency format embedded in a Singlish sentence</t>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'AUD 1200' is a currency amount embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2078,34 +2684,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>api heta 6:00AM yana ona, ready wela inna.</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>අපි හෙට 6:00AM ට යන්න ඕනා, ready වෙලා ඉන්න.</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>අපි හෙට 6:00AM යන ඕන, ready වෙලා ඉන්න.</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>interview eka 10:30AM ta, oya ready da?</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>interview එක 10:30AM ට, ඔයා ready ද?</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>interview එක 10:30ට, ඔයා ready ද?</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Inputs with Time Formats</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: '6:00AM' is a time format embedded in a Singlish sentence</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: '10:30AM' is a time format embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2120,19 +2726,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>lecture eka 2:30pm walata withurak da, ada awwa naha.</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>lecture එක 2:30pm වලටයි, අද ආවේ නෑ.</t>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>train ekk 4:15pm ta pitath wenawa, early yanna.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>train එක 4:15pm ට පිටත් වෙනවා, early යන්න.</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>lecture එක 2:30pm වලට විතරක් ද, අද අව්ව නැහැ.</t>
+          <t>train එකා 4:15pm ට පිටත් වෙනවා, ඉක්මනට යන්න.</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2140,14 +2746,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Inputs with Time Formats</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: '2:30pm' is a time format embedded in a Singlish sentence</t>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: '4:15pm' is a time format embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2162,34 +2768,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>mage birthday eka March 22 wenuwan, mokak hadamu?</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>මගේ birthday එක March 22 ට, මොකක් හදමු?</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>මගේ birthday එක March 22 වෙනුවන්, මොකක් හදමු?</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>project submission eka June 30, time naha.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>project submission එක June 30, time නෑ.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>project submission එක June 30ටයිම් නැහැ.</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Inputs with Dates</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'March 22' is a date embedded in a Singlish sentence</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'June 30' is a date embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2204,34 +2810,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>submit karanna ona 2026-05-10 ta, api hurry wela.</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10 ට submit කරන්න ඕනා, අපි hurry වෙලා.</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>submit කරන්න ඕන 2026-05-10 ට, අපි hurry වෙලා.</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Oyage birthday 2026-08-14 da, correct da?</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ birthday 2026-08-14 ද, correct ද?</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ birthday 2026-08-14 ද, correct ද?</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Inputs with Dates</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: '2026-05-10' is a date in numeric format embedded in a Singlish sentence</t>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: '2026-08-14' is a date in numeric format embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2246,34 +2852,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>e kade tikka 2kg wage innawa, ganin godak naha.</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>ඒ කේළෑ ටිකක් 2kg වගේ ඇති, ගාන ගොඩක් නෑ.</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ඒ කඩේ ටික 2kg වගේ ඉන්නවා, ගනින් ගොඩක් නැහැ.</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Mage weight eka 5kg kin wadi una, gym yanna one.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>මගේ weight එක 5kg කින් වැඩි වුණා, gym යන්න ඕනේ.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>මගේ weight එක 5kg කින් වාඩි උනා, gym යන්න ඕනේ.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Inputs with Unit of Measurements</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: '2kg' is a unit of measurement embedded in a Singlish sentence</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: '5kg' is a unit of measurement embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2288,34 +2894,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>classroom eka square feet 500 witharai, gediya.</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>classroom එක square feet 500 විතරයි, ගොඩක් gediya.</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>classroom එක square feet 500 විතරයි, ගෙඩිය.</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ape gedara pool eka feet 20 witharai, podi.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>අපේ ගෙදර pool එක feet 20 විතරයි, පොඩියි.</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>අපේ ගෙදර pool එක feet 20 විතරයි, පොඩි.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Inputs with Unit of Measurements</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'square feet 500' is a measurement unit phrase embedded in a Singlish sentence</t>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'feet 20' is a unit of measurement embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2330,34 +2936,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Aney bro, meka iskole eke weda thanama mokada?</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>අනේ bro, මේක ඉස්කෝලේ වැඩ විතරක් මොකද?</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>අනේ bro, මේක ඉස්කෝලේ එකේ වැඩ තනාම මොකද?</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Yako, uba danne naha da api kiwwe kiyala, pissu da?</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>යකෝ, උඹ දන්නේ නෑ ද අපි කිව්වේ කියලා, පිස්සු ද?</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>යකෝ, උඹ දන්නේ නැහැ ද අපි කිව්වේ කියලා, පිස්සු ද?</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Inputs with Slang and Casual Phrasing</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: 'bro' is slang and 'aney' is a casual Sinhala expression used informally</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'Yako' and 'pissu' are casual slang expressions common in informal Sinhala chat</t>
         </is>
       </c>
     </row>
@@ -2372,39 +2978,39 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Uba gediye hitiya, ammagen gahanna giyada?</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>උඹ ගෙදර හිටියා, අම්මාගෙන් ගහනවා ගියද?</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>උඹ ගෙඩියේ හිටියා, අම්මගෙන් ගහන්න ගියාද?</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Nangi meka niyamai, pure fire, bohoma hodai aiye.</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>නංගි මේක නියමයි, pure fire, බොහොම හොඳයි අයියේ.</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>නංගි මේක නියමයි, pure fire, බොහොම හොඳයි අයියෙ.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Inputs with Slang and Casual Phrasing</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Uba' is slang for 'you' and the phrasing is very casual and colloquial</t>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: 'pure fire' is a slang phrase meaning something is excellent, used casually in Singlish</t>
         </is>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Neg_0045</t>
         </is>
@@ -2414,34 +3020,34 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>mama email ekak ewwa info@sliit.lk ekata, baluwa da?</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>මම email එකක් එව්වා info@sliit.lk එකට, බැලුවා ද?</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>මම email එකක් එව්වා info@sliit.lk ටට, බැලුවා ද?</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>mata link eka ewwa: https://forms.gle/abc123, fill karanna.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>මට link එක එව්වා: https://forms.gle/abc123, fill කරන්න.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>මට link එක එව්වා: https://ෆොර්ම්ස්.ගී/abc123, fill කරන්න.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Online Identifiers in Singlish</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Rationale: An email address 'info@sliit.lk' is an online identifier embedded in Singlish; the system incorrectly adds extra characters around the email address</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: 'https://forms.gle/abc123' is a URL (online identifier) embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2456,19 +3062,19 @@
           <t>M</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>@Sampath ayya oyata group eke message ekak ewwa.</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>@Sampath අයියා ඔයාට group එකේ message එකක් එව්වා.</t>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>@Kasun_lk oyage DM ekak ewwa, check karanna.</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>@Kasun_lk ඔයාට DM එකක් එව්වා, check කරන්න.</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>@සම්පත් අයියා ඔයාට group එකේ message එකක් එව්වා.</t>
+          <t>@Kasun_lk ඔයාගේ DM එකක් ආවා, check කරන්න.</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -2476,14 +3082,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Online Identifiers in Singlish</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: '@Sampath' is a social media mention (online identifier) embedded in a Singlish sentence</t>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: '@Kasun_lk' is a social media handle (online identifier) embedded in the Singlish sentence</t>
         </is>
       </c>
     </row>
@@ -2498,34 +3104,34 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Mama godak thesanei 😔 mokak karanneda.</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>මම ගොඩක් තෙහෙට්ටු 😔 මොකක් කරන්නද.</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>මම ගොඩක් තේසනයි  මොකක් කරන්නේද.</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Godak stressful day ekak 😩 tikak rest gannm.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ගොඩක් stressful day එකක් 😩 ටිකක් rest ගන්නම්.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ගොඩක් stressful day එකක්  ටිකක් rest ගන්නම්.</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Inputs Containing Emojis</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>Rationale: The emoji 😔 is embedded within a Singlish sentence expressing tiredness</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Rationale: The emoji 😩 is embedded within a Singlish sentence expressing a stressful day</t>
         </is>
       </c>
     </row>
@@ -2540,34 +3146,34 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Niyamayata gehuwa 🔥 api janthuwai.</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>නියාමට ගැහුවා 🔥 අපි ජාන්තුයි.</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>නියමයට ගැහුවා 🔥 අපි ජන්තුවයි.</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Api finally 🎉 exam pass wuna machan!</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>අපි finally 🎉 exam pass වුනා මචං!</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>අපි finally 🤣 exam pass වුණා මචන්!</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Inputs Containing Emojis</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: The fire emoji 🔥 is embedded in a Singlish sentence expressing excitement</t>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: The party emoji 🎉 is embedded in a Singlish sentence expressing excitement about passing</t>
         </is>
       </c>
     </row>
@@ -2582,19 +3188,19 @@
           <t>L</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Machan mama heta 8:00AM walata office yana ona, Rs. 500 taxi eken yannam. Boss kiuwwa ASAP wanna kiyala. Oya niyeda api eka office eke innawa? Karunakarala reply karanna.</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>මචං මම හෙට 8:00AM ට office යන්න ඕනා, Rs. 500 taxi එකෙන් යන්නම්. Boss කිව්වා ASAP එන්න කියලා. ඔයා නේද අපි ඒ office එකේ ඉන්නේ? කරුණාකරලා reply කරන්න.</t>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Bro ada uni eke presentation eka 2:00PM ta thiyenawa, PowerPoint eka ready da? Slides 15k witharai hadanna kiwwa lecturer. ASAP check karanna, group eke @Dulaj ayya kiyanakam inna.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Bro අද uni එකේ presentation එක 2:00PM ට තියෙනවා, PowerPoint එක ready ද? Slides 15k විතර හදන්න කිව්වා lecturer. ASAP check කරන්න, group එකේ @Dulaj අයියා කියනකම් ඉන්න.</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>මචං මම හෙට 8:00AM වලට office යන ඕන, Rs. 500 taxi එකෙන් යන්නම්. Boss කිව්වා ASAP වන්න කියලා. ඔයා නේද අපි ඒ office එකේ ඉන්නේ? කරුණාකරලා reply කරන්න.</t>
+          <t>Bro අද uni එකේ presentation එක 2:00PM ට තියෙනවා, PowerPoint එක ready ද? Slides 15ක් විතර හදන්න කිව්වා lecturer. ASAP check කරන්න, group එකේ @Dulaj අයියා කියනකම් ඉන්න.</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2602,14 +3208,14 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Question forms | Inputs with Time Formats | Inputs with Currency | English Abbreviations/Acronyms | Isolated English Word Insertions in Singlish</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Evidence: ends with a question; '8:00AM' is a time format; 'Rs. 500' is currency; 'ASAP' is an acronym; 'office', 'taxi', 'Boss' are isolated English words in Singlish</t>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Question forms | Inputs with Time Formats | English Clipped Forms in Singlish | Inputs with Numbers and Numeric Suffixes | English Abbreviations/Acronyms | Online Identifiers in Singlish</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Evidence: ends with a question; '2:00PM' is a time format; 'uni' is a clipped form of University; '15k' is a number with suffix; 'ASAP' is an acronym; '@Dulaj' is an online identifier</t>
         </is>
       </c>
     </row>
@@ -2624,19 +3230,19 @@
           <t>L</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Bro, ada Colombo 7 nattam karala Dilshan ayya saha api meet wuwa. Google Maps eken route eka baluwe naha, ezz 😂. Then api McDonald's eke kawa, bill eka LKR 3500 wuwa. Hoda dawasak neda!</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Bro, අද Colombo 7 ට plan කරලා Dilshan අයියා සහ අපි meet වුණා. Google Maps ගාව route එක බැලුවේ නෑ, ezz 😂. ඊට පස්සේ අපි McDonald's ගිහින් කෑවා, bill එක LKR 3500 වුණා. හොඳ දවසක් නේද!</t>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Nangi heta Colombo 3 ta yamu, Rs. 2000 witharai budget. Ruwan aiya kiuwwa Uber eken yanna, cheaper wela. Map eke check karuwa, miles 8k witharai wage 😅. Oya CV eka update kala da job eke apply karanna?</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>නංගි හෙට Colombo 3 ට යමු, Rs. 2000 විතරයි budget. Ruwan අයියා කිව්වා Uber එකෙන් යන්න, cheaper වෙලා. Map එකේ check කරුවා, miles 8k විතර වගේ 😅. ඔයා CV එක update කළා ද job එකේ apply කරන්න?</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Bro, අද Colombo 7 නට්ටම් කරලා Dilshan අයියා සහ අපි meet වුවා. Google Maps එකෙන් route එක බැලුවේ නැහැ, ezz 😂. ඊට පස්සේ අපි McDonald's එකේ කෑවා, bill එක LKR 3500 වුවා. හොඳ දවසක් නේද!</t>
+          <t>නංගි හෙට Colombo 3 ට යමු, Rs. 2000 විතරයි budget. Ruwan අයියා කිව්වා Uber එකෙන් යන්න, cheaper. Map ගාව check කරලා, miles 8k විතර 😅. ඔය CV ඒක update කළාද job ගාට apply කරන්ද?</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2644,18 +3250,19 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Inputs with Slang and Casual Phrasing | Place Names Embedded in Singlish | Person Names Embedded in Singlish | Platform/App Names in Singlish | Inputs with Currency | Inputs Containing Emojis</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Rationale: 'Bro' and 'nattam' are slang; 'Colombo 7' is a place name; 'Dilshan' is a person name; 'Google Maps' and 'McDonald's' are app/brand names; 'LKR 3500' is currency; 😂 is an emoji</t>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Question forms | Place Names Embedded in Singlish | Inputs with Currency | Platform/App Names in Singlish | Person Names Embedded in Singlish | Inputs with Unit of Measurements | Inputs Containing Emojis | English Abbreviations/Acronyms</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Rationale: ends with a question; 'Colombo 3' is a place name; 'Rs. 2000' is currency; 'Uber' is an app name; 'Ruwan' is a person name; 'miles 8k' is a measurement; 😅 is an emoji; 'CV' is an acronym</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup usePrinterDefaults="0"/>
 </worksheet>
 </file>